--- a/processing/data_processing/cross_table.xlsx
+++ b/processing/data_processing/cross_table.xlsx
@@ -490,7 +490,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>quantum support vector classifier</t>
+          <t>variational quantum classifier</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -500,7 +500,7 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -512,7 +512,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>variational quantum classifier</t>
+          <t>quantum support vector classifier</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -522,7 +522,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -578,17 +578,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>federated quantum tensor network</t>
+          <t>not specified</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -600,20 +600,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>quantum k-nearest neighbors</t>
+          <t>quantum tensor networks</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -622,20 +622,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quantum tensor networks</t>
+          <t>quantum k-nearest neighbors</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -644,14 +644,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>quantum approximate optimization algorithm-inspired ansatz circuit</t>
+          <t>federated quantum tensor network</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -660,29 +660,29 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>quantum long short-term memory</t>
+          <t>quantum approximate optimization algorithm-inspired ansatz circuit</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -710,20 +710,20 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>qcc-net</t>
+          <t>quantum recurrent neural network</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hybrid quantum–classical neural network</t>
+          <t>quantum self-attention model</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -742,10 +742,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -754,42 +754,42 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time-series hamiltonian kernel</t>
+          <t>dressed quantum circuit</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>quantum self-attention model</t>
+          <t>qcc-net</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -798,20 +798,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>quantum recurrent neural network</t>
+          <t>quantum long short-term memory</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -820,23 +820,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dressed quantum circuit</t>
+          <t>time-series hamiltonian kernel</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
